--- a/cucumber-for-appian/src/test/resources/testdata/End2End/08_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/08_NovatedApp_End2End.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
   <si>
     <t>TC ID</t>
   </si>
@@ -155,6 +155,9 @@
     <t>EOL Date</t>
   </si>
   <si>
+    <t>EOL Last Odometer Reading</t>
+  </si>
+  <si>
     <t>Days Remaining until EOL</t>
   </si>
   <si>
@@ -167,12 +170,18 @@
     <t>Fuel Card</t>
   </si>
   <si>
+    <t>47410</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Lost</t>
   </si>
   <si>
+    <t>21 May 2026</t>
+  </si>
+  <si>
     <t>REQ-689</t>
   </si>
   <si>
@@ -188,124 +197,233 @@
     <t>Mr</t>
   </si>
   <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Huts</t>
+  </si>
+  <si>
+    <t>18/05/1994</t>
+  </si>
+  <si>
+    <t>0423358183</t>
+  </si>
+  <si>
+    <t>awhuts@gmail.com.test</t>
+  </si>
+  <si>
+    <t>Your Residential Address *</t>
+  </si>
+  <si>
+    <t>ESSO Australia Pty Ltd</t>
+  </si>
+  <si>
+    <t>CZB960</t>
+  </si>
+  <si>
+    <t>KIA CARNIVAL</t>
+  </si>
+  <si>
+    <t>25 Sept 2026</t>
+  </si>
+  <si>
+    <t>2 Jul 2026</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>${TC001.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC001.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC001.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC001.Odometer}</t>
+  </si>
+  <si>
+    <t>${TC001.Fuel Provider}</t>
+  </si>
+  <si>
+    <t>${TC001.Delivery Address}</t>
+  </si>
+  <si>
+    <t>${TC001.Request Submission Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Last Update Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Request Subtype}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Salutation}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver First Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Last Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Date of Birth}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Mobile Phone}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Email}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Your Residential Address}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Employer Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle number}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle name}</t>
+  </si>
+  <si>
+    <t>${TC001.Lease End Date}</t>
+  </si>
+  <si>
+    <t>No Number Info</t>
+  </si>
+  <si>
+    <t>FTJ63Y</t>
+  </si>
+  <si>
+    <t>VOLVO XC40</t>
+  </si>
+  <si>
+    <t>11 Feb 2026</t>
+  </si>
+  <si>
+    <t>100705</t>
+  </si>
+  <si>
     <t>David</t>
   </si>
   <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>30/10/1997</t>
-  </si>
-  <si>
-    <t>0499999999</t>
-  </si>
-  <si>
-    <t>visionpro101@gmail.com.test</t>
-  </si>
-  <si>
-    <t>Your Residential Address *</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CPK418</t>
-  </si>
-  <si>
-    <t>VOLVO C40</t>
-  </si>
-  <si>
-    <t>25 Sept 2026</t>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>${TC001.Last Odometer Reading}</t>
-  </si>
-  <si>
-    <t>${TC001.New Odometer}</t>
-  </si>
-  <si>
-    <t>${TC001.Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Last Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Reference Number}</t>
-  </si>
-  <si>
-    <t>${TC001.Odometer}</t>
-  </si>
-  <si>
-    <t>${TC001.Fuel Provider}</t>
-  </si>
-  <si>
-    <t>${TC001.Delivery Address}</t>
-  </si>
-  <si>
-    <t>${TC001.Request Submission Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Last Update Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Request Subtype}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Salutation}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver First Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Last Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Date of Birth}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Mobile Phone}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Email}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Your Residential Address}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Employer Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Vehicle}</t>
-  </si>
-  <si>
-    <t>${TC001.Vehicle number}</t>
-  </si>
-  <si>
-    <t>${TC001.Vehicle name}</t>
-  </si>
-  <si>
-    <t>${TC001.Lease End Date}</t>
-  </si>
-  <si>
-    <t>No Number Info</t>
+    <t>Cracknell</t>
+  </si>
+  <si>
+    <t>13/01/1988</t>
+  </si>
+  <si>
+    <t>0409999999</t>
+  </si>
+  <si>
+    <t>david.cracknell@keyton.com.au.test</t>
+  </si>
+  <si>
+    <t>KEYTON MANAGEMENT SERVICES PTY LTD AS TRUSTEE FOR KEYTON MANAGEMENT SERVICES TRUST</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1IQP317</t>
+  </si>
+  <si>
+    <t>TOYOTA HILUX</t>
+  </si>
+  <si>
+    <t>25 Jun 2026</t>
+  </si>
+  <si>
+    <t>14484</t>
+  </si>
+  <si>
+    <t>Jenson</t>
+  </si>
+  <si>
+    <t>Cooke</t>
+  </si>
+  <si>
+    <t>06/05/1977</t>
+  </si>
+  <si>
+    <t>396666544</t>
+  </si>
+  <si>
+    <t>jensonc@youi.com.test</t>
+  </si>
+  <si>
+    <t>Youi Pty Ltd</t>
+  </si>
+  <si>
+    <t>10 Mar 2026</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>1XZ2BI</t>
+  </si>
+  <si>
+    <t>MG MG ZS</t>
+  </si>
+  <si>
+    <t>30 May 2026</t>
+  </si>
+  <si>
+    <t>24801</t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>04/05/1990</t>
+  </si>
+  <si>
+    <t>333366555</t>
+  </si>
+  <si>
+    <t>stephen.jackson@exxonmobil.com.test</t>
+  </si>
+  <si>
+    <t>19 Feb 2026</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -943,7 +1061,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -964,6 +1082,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1307,35 +1428,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.7" customWidth="1"/>
-    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.775" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.775" customWidth="1"/>
-    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="23.775" customWidth="1"/>
-    <col min="11" max="11" width="17.225" customWidth="1"/>
-    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
-    <col min="23" max="23" width="20.7" customWidth="1"/>
-    <col min="24" max="24" width="24.6" customWidth="1"/>
-    <col min="25" max="25" width="29.8" customWidth="1"/>
-    <col min="26" max="27" width="24.5" customWidth="1"/>
-    <col min="42" max="42" width="13.1" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
+    <col min="2" max="2" customWidth="true" width="20.7"/>
+    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
+    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
+    <col min="6" max="6" customWidth="true" width="16.775"/>
+    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
+    <col min="8" max="8" customWidth="true" width="21.775"/>
+    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
+    <col min="10" max="10" customWidth="true" width="23.775"/>
+    <col min="11" max="11" customWidth="true" width="17.225"/>
+    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
+    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
+    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
+    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
+    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
+    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
+    <col min="18" max="22" customWidth="true" width="19.1083333333333"/>
+    <col min="23" max="23" customWidth="true" width="20.7"/>
+    <col min="24" max="24" customWidth="true" width="24.6"/>
+    <col min="25" max="25" customWidth="true" width="29.8"/>
+    <col min="26" max="27" customWidth="true" width="24.5"/>
+    <col min="42" max="43" customWidth="true" width="13.1"/>
+    <col min="44" max="44" customWidth="true" width="12.5"/>
+    <col min="45" max="45" customWidth="true" width="20.2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="69" spans="1:44">
+    <row r="1" s="1" customFormat="1" ht="69" spans="1:46">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1465,244 +1587,272 @@
       <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="AS1" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="55.2" spans="1:44">
+    <row r="2" s="2" customFormat="1" ht="55.2" spans="1:46">
       <c r="A2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <f>C2+1</f>
+        <v>24802.0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <f>D2</f>
+        <v>24802.0</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="T2" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="U2" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>0 km</v>
+        <v>24,802 km</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="X2" s="7"/>
       <c r="Y2" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>David Stewart</v>
+        <v>Stephen Jackson</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>VOLVO C40 - CPK418</v>
+        <v>MG MG ZS - 1XZ2BI</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AO2" s="7"/>
-      <c r="AP2" s="7"/>
-      <c r="AQ2" s="7"/>
+      <c r="AP2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ2" s="7" t="str">
+        <f>TEXT(C2,"#,##0")</f>
+        <v>24,801</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AS2" s="7" t="str">
+        <f>"Intend to Terminate on "&amp;TEXT(T2,"dd mmmm yyyy")</f>
+        <v>Intend to Terminate on 19 February 2026</v>
+      </c>
+      <c r="AT2" s="8"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:44">
+    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:46">
       <c r="A3" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AN3" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
+      <c r="AR3" s="4"/>
+      <c r="AS3" s="4"/>
     </row>
-    <row r="5" spans="1:44">
-      <c r="E5" s="8"/>
+    <row r="5" spans="1:46">
+      <c r="E5" s="9"/>
     </row>
-    <row r="10" spans="1:44">
-      <c r="U10" s="9"/>
+    <row r="10" spans="1:46">
+      <c r="U10" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
